--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484020_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484020_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7607</v>
+        <v>8.2912</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0383</v>
+        <v>6.3444</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7224</v>
+        <v>1.9469</v>
       </c>
       <c r="G2" t="n">
         <v>5.5351</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2981</v>
+        <v>0.2324</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3288</v>
+        <v>0.6349</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.627</v>
+        <v>-0.4025</v>
       </c>
       <c r="V2" t="n">
         <v>0.9367</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7591</v>
+        <v>5.3559</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0386</v>
+        <v>2.2426</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7205</v>
+        <v>3.1133</v>
       </c>
       <c r="G3" t="n">
         <v>3.1771</v>
@@ -688,13 +688,13 @@
         <v>2.579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.747</v>
+        <v>-0.1502</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0566</v>
+        <v>0.1475</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6904</v>
+        <v>-0.2976</v>
       </c>
       <c r="V3" t="n">
         <v>0.742</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7513</v>
+        <v>4.6283</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8877</v>
+        <v>1.933</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8636</v>
+        <v>2.6953</v>
       </c>
       <c r="G4" t="n">
         <v>2.6246</v>
@@ -766,13 +766,13 @@
         <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6586</v>
+        <v>0.5356</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4366</v>
+        <v>0.4819</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2221</v>
+        <v>0.0537</v>
       </c>
       <c r="V4" t="n">
         <v>0.6745</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5102</v>
+        <v>4.6056</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7224</v>
+        <v>1.3969</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7878</v>
+        <v>3.2087</v>
       </c>
       <c r="G5" t="n">
         <v>1.9982</v>
@@ -844,13 +844,13 @@
         <v>2.9758</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2101</v>
+        <v>-0.1148</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8501</v>
+        <v>-0.1756</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.36</v>
+        <v>0.0608</v>
       </c>
       <c r="V5" t="n">
         <v>0.9367</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0796</v>
+        <v>2.5899</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3498</v>
+        <v>0.1689</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7298</v>
+        <v>2.421</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0146</v>
+        <v>1.9671</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4192</v>
+        <v>0.8722</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4046</v>
+        <v>1.0948</v>
       </c>
       <c r="J6" t="n">
-        <v>0.369</v>
+        <v>2.6543</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7243</v>
+        <v>0.6462</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3553</v>
+        <v>2.0081</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3545</v>
+        <v>-0.6872</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6949</v>
+        <v>0.226</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0493</v>
+        <v>-0.9133</v>
       </c>
       <c r="P6" t="n">
         <v>2.3806</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3806</v>
+        <v>3.5709</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1489</v>
+        <v>-0.214</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9807</v>
+        <v>-0.2833</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1682</v>
+        <v>0.0693</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4645</v>
+        <v>-1.5437</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-1.0118</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4645</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4769</v>
+        <v>2.5171</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0839</v>
+        <v>0.6725</v>
       </c>
       <c r="F7" t="n">
-        <v>2.393</v>
+        <v>1.8446</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9671</v>
+        <v>0.7048</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8722</v>
+        <v>0.0959</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0948</v>
+        <v>0.6089</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6543</v>
+        <v>0.1509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6462</v>
+        <v>-0.0499</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0081</v>
+        <v>0.2008</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6872</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.226</v>
+        <v>0.1458</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9133</v>
+        <v>0.4081</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.5709</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3271</v>
+        <v>0.5427</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3683</v>
+        <v>0.5215</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0413</v>
+        <v>0.0212</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5437</v>
+        <v>0.476</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.0118</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.532</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4533</v>
+        <v>2.3458</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4684</v>
+        <v>0.9246</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9849</v>
+        <v>1.4212</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7048</v>
+        <v>0.0146</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0959</v>
+        <v>2.4192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6089</v>
+        <v>-2.4046</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1509</v>
+        <v>0.369</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0499</v>
+        <v>1.7243</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2008</v>
+        <v>-1.3553</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5538999999999999</v>
+        <v>-0.3545</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1458</v>
+        <v>0.6949</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4081</v>
+        <v>-1.0493</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4789</v>
+        <v>0.4152</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3175</v>
+        <v>0.5556</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1615</v>
+        <v>-0.1404</v>
       </c>
       <c r="V8" t="n">
-        <v>0.476</v>
+        <v>-0.4645</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.476</v>
+        <v>-0.4645</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1444</v>
+        <v>1.1708</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.217</v>
+        <v>-0.8259</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3614</v>
+        <v>1.9967</v>
       </c>
       <c r="G9" t="n">
         <v>0.0722</v>
@@ -1156,13 +1156,13 @@
         <v>2.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0505</v>
+        <v>-0.0241</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.947</v>
+        <v>0.5823</v>
       </c>
       <c r="V9" t="n">
         <v>-0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5547</v>
+        <v>0.5609</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0147</v>
+        <v>0.0771</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5399</v>
+        <v>0.4838</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3427</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2347</v>
+        <v>0.2409</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3685</v>
+        <v>0.4308</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1338</v>
+        <v>-0.1899</v>
       </c>
       <c r="V10" t="n">
         <v>0.266</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1113</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5251</v>
+        <v>0.0999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4138</v>
+        <v>-0.1894</v>
       </c>
       <c r="G11" t="n">
         <v>1.9219</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4671</v>
+        <v>0.2664</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2301</v>
+        <v>0.805</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.763</v>
+        <v>-0.5386</v>
       </c>
       <c r="V11" t="n">
         <v>-1.881</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3563</v>
+        <v>-1.9474</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3197</v>
+        <v>-2.3448</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9634</v>
+        <v>0.3974</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7894</v>
+        <v>-1.2039</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9124</v>
+        <v>-1.2246</v>
       </c>
       <c r="I12" t="n">
-        <v>0.123</v>
+        <v>0.0207</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2122</v>
+        <v>-1.4153</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.655</v>
+        <v>-1.2999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5572</v>
+        <v>-0.1154</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4228</v>
+        <v>0.2114</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2574</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6802</v>
+        <v>0.136</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4374</v>
+        <v>0.1176</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8843</v>
+        <v>0.2608</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5531</v>
+        <v>-0.1432</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.266</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5542</v>
+        <v>-2.0909</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9797</v>
+        <v>-3.8299</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4255</v>
+        <v>1.739</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2039</v>
+        <v>-2.7894</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2246</v>
+        <v>-2.9124</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0207</v>
+        <v>0.123</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4153</v>
+        <v>-3.2122</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2999</v>
+        <v>-2.655</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1154</v>
+        <v>-0.5572</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2114</v>
+        <v>0.4228</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.2574</v>
       </c>
       <c r="O13" t="n">
-        <v>0.136</v>
+        <v>0.6802</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4892</v>
+        <v>0.7029</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3741</v>
+        <v>0.3742</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1151</v>
+        <v>0.3287</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.266</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.266</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.691</v>
+        <v>27.9378</v>
       </c>
       <c r="E14" t="n">
-        <v>5.612500000000002</v>
+        <v>6.859299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>21.0784</v>
+        <v>21.0785</v>
       </c>
       <c r="G14" t="n">
         <v>13.6796</v>
       </c>
       <c r="H14" t="n">
-        <v>6.3274</v>
+        <v>6.327399999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>7.352000000000001</v>
+        <v>7.352</v>
       </c>
       <c r="J14" t="n">
         <v>13.3135</v>
       </c>
       <c r="K14" t="n">
-        <v>4.115900000000001</v>
+        <v>4.1159</v>
       </c>
       <c r="L14" t="n">
-        <v>9.197600000000001</v>
+        <v>9.197600000000003</v>
       </c>
       <c r="M14" t="n">
         <v>0.3660999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>22.8143</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3036</v>
+        <v>2.5506</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8999</v>
+        <v>3.1469</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5961</v>
+        <v>-0.5961999999999998</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1872</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0214</v>
+        <v>1.0812</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.4048</v>
+        <v>1.2581</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4262</v>
+        <v>-0.1769</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.091</v>
+        <v>1.8547</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0813</v>
+        <v>0.1303</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1723</v>
+        <v>1.7244</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8005</v>
+        <v>3.5435</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8808</v>
+        <v>0.3682</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0803</v>
+        <v>3.1753</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7095</v>
+        <v>-1.6888</v>
       </c>
       <c r="N15" t="n">
-        <v>0.962</v>
+        <v>-0.2379</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2526</v>
+        <v>-1.4509</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9838</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8302</v>
+        <v>-0.6589</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1054</v>
+        <v>-0.7821</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7248</v>
+        <v>0.1232</v>
       </c>
       <c r="V15" t="n">
-        <v>0.266</v>
+        <v>1.4724</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>1.4724</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4381</v>
+        <v>-1.2378</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5439000000000001</v>
+        <v>-3.3231</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9821</v>
+        <v>2.0853</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8547</v>
+        <v>-0.091</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1303</v>
+        <v>0.0813</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7244</v>
+        <v>-0.1723</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5435</v>
+        <v>-0.8005</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3682</v>
+        <v>-0.8808</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1753</v>
+        <v>0.0803</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6888</v>
+        <v>0.7095</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2379</v>
+        <v>0.962</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4509</v>
+        <v>-0.2526</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5871</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.9758</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1782</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4963</v>
+        <v>0.1871</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6819</v>
+        <v>0.3839</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6709</v>
+        <v>-1.4226</v>
       </c>
       <c r="E17" t="n">
         <v>-2.9794</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3086</v>
+        <v>1.5568</v>
       </c>
       <c r="G17" t="n">
         <v>-2.0858</v>
@@ -1780,13 +1780,13 @@
         <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0612</v>
+        <v>0.187</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0566</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0046</v>
+        <v>0.2436</v>
       </c>
       <c r="V17" t="n">
         <v>0.6745</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2303</v>
+        <v>-1.5025</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2022</v>
+        <v>-2.3747</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0281</v>
+        <v>0.8723</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1211</v>
+        <v>-0.9187</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0798</v>
+        <v>-1.5327</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2009</v>
+        <v>0.614</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.5783</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7258</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>1.1322</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9674</v>
+        <v>-1.4969</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.646</v>
+        <v>-0.9788</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3214</v>
+        <v>-0.5182</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7125</v>
+        <v>0.2097</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0566</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6559</v>
+        <v>0.306</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5756</v>
+        <v>-2.0662</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0683</v>
+        <v>-0.2022</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6439</v>
+        <v>-1.864</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2154</v>
+        <v>-1.1211</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7514999999999999</v>
+        <v>0.0798</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4639</v>
+        <v>-1.2009</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2366</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2366</v>
+        <v>0.7258</v>
       </c>
       <c r="L19" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.9674</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.646</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.3214</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.3968</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5952</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.5484</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.0566</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.4918</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>-1.9788</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.5148</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-1.4639</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-1.7855</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-2.1822</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3968</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.2306</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.6892</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.4586</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.1947</v>
-      </c>
       <c r="W19" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6554</v>
+        <v>-2.6133</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.191</v>
+        <v>-2.6849</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5356</v>
+        <v>0.0716</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9187</v>
+        <v>-2.4905</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5327</v>
+        <v>-0.9177</v>
       </c>
       <c r="I20" t="n">
-        <v>0.614</v>
+        <v>-1.5728</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5783</v>
+        <v>-1.9198</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5995</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1322</v>
+        <v>-1.3202</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4969</v>
+        <v>-0.5707</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9788</v>
+        <v>-0.3181</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5182</v>
+        <v>-0.2526</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1822</v>
+        <v>-0.1984</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9432</v>
+        <v>-0.2537</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9125</v>
+        <v>-0.5667</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0307</v>
+        <v>0.3131</v>
       </c>
       <c r="V20" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="W20" t="n">
-        <v>-0.6745</v>
-      </c>
       <c r="X20" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9713</v>
+        <v>-3.4158</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.991</v>
+        <v>-4.4177</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0197</v>
+        <v>1.002</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4905</v>
+        <v>-1.3134</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9177</v>
+        <v>-0.4234</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5728</v>
+        <v>-0.8901</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9198</v>
+        <v>-0.8376</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5995</v>
+        <v>-0.7248</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3202</v>
+        <v>-0.1128</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5707</v>
+        <v>-0.4758</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3181</v>
+        <v>0.3014</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2526</v>
+        <v>-0.7772</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3968</v>
+        <v>-2.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1984</v>
+        <v>-4.1661</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6116</v>
+        <v>-0.3925</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8728</v>
+        <v>-0.2833</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2612</v>
+        <v>-0.1092</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="W21" t="n">
+        <v>0.8692</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.266</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9319</v>
+        <v>-3.442</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8259</v>
+        <v>-0.85</v>
       </c>
       <c r="F22" t="n">
-        <v>0.894</v>
+        <v>-2.592</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3134</v>
+        <v>-2.2154</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4234</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8901</v>
+        <v>-1.4639</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8376</v>
+        <v>-0.2366</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7248</v>
+        <v>-0.2366</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1128</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4758</v>
+        <v>-1.9788</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3014</v>
+        <v>-0.5148</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7772</v>
+        <v>-1.4639</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.579</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1661</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9086</v>
+        <v>0.3642</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6914</v>
+        <v>0.7709</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2172</v>
+        <v>-0.4068</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8692</v>
+        <v>0.1947</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8692</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1212</v>
+        <v>-4.3269</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3975</v>
+        <v>-2.9077</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7237</v>
+        <v>-1.4193</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6176</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2937</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4398</v>
+        <v>0.9297</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1462</v>
+        <v>-0.8418</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0118</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1177</v>
+        <v>-6.3846</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6989</v>
+        <v>-2.5969</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4187</v>
+        <v>-3.7877</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6809</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7572</v>
+        <v>0.4903</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4479</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3093</v>
+        <v>-0.0596</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0118</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.691</v>
+        <v>-25.3305</v>
       </c>
       <c r="E25" t="n">
         <v>-21.0785</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.612399999999999</v>
+        <v>-4.2519</v>
       </c>
       <c r="G25" t="n">
         <v>-13.6797</v>
@@ -2377,7 +2377,7 @@
         <v>-7.3522</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.366</v>
+        <v>-0.3659999999999998</v>
       </c>
       <c r="K25" t="n">
         <v>-2.2115</v>
@@ -2404,13 +2404,13 @@
         <v>9.9193</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3036</v>
+        <v>0.05669999999999992</v>
       </c>
       <c r="T25" t="n">
         <v>0.5961000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8998</v>
+        <v>-0.5394000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>1.1872</v>
